--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260904.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260904.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>6,089,000</t>
+          <t>6,118,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.20%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>10,424,000</t>
+          <t>10,467,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>3.67%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,637,000</t>
+          <t>21,729,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6,254,000</t>
+          <t>6,282,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>48,740,000</t>
+          <t>48,962,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>35,649,000</t>
+          <t>35,782,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
@@ -743,78 +743,78 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>562,000</t>
+          <t>564,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>10,156,000</t>
+          <t>20,733,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>20,627,000</t>
+          <t>10,202,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>3,948,000</t>
+          <t>4,063,341,193</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -831,78 +831,78 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>11,407,000</t>
+          <t>11,465,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>202609WTX</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>115/09台股期貨</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>3,948,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>202609WTX</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>115/09台股期貨</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>26,162,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>34,731,000</t>
+          <t>22,876,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -919,183 +919,183 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,739,000</t>
+          <t>6,769,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>3,519,820,763</t>
+          <t>34,858,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>37,749,000</t>
+          <t>26,264,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>22,764,000</t>
+          <t>37,920,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>32,953,000</t>
+          <t>9,637,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>9,588,000</t>
+          <t>33,103,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,217,000</t>
+          <t>9,594,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9,548,000</t>
+          <t>4,364,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>4,345,000</t>
+          <t>2,225,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,883,000</t>
+          <t>2,893,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>4,761,400</t>
+          <t>4,784,400</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>14,264,000</t>
+          <t>14,346,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,213,000</t>
+          <t>15,295,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>41,037,000</t>
+          <t>41,257,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>18,002,000</t>
+          <t>18,088,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,632,081,747</t>
+          <t>2,703,281,747</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1271,100 +1271,100 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>6,630,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,179,000</t>
+          <t>9,700,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,984,000</t>
+          <t>6,199,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>9,652,000</t>
+          <t>7,920,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>7,883,000</t>
+          <t>4,995,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>24,954,004</t>
+          <t>25,054,004</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -1425,29 +1425,29 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,241,000</t>
+          <t>10,287,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>14,405,000</t>
+          <t>16,725,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,44 +1459,44 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>9,303,000</t>
+          <t>14,476,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>16,642,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2,298,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>8,918,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>48,160,000</t>
+          <t>48,390,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>52,656,000</t>
+          <t>18,948,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,22 +1635,22 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>18,852,000</t>
+          <t>52,799,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,586,000</t>
+          <t>1,593,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>16,762,000</t>
+          <t>16,823,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>18,415,000</t>
+          <t>18,491,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>18,144,000</t>
+          <t>18,224,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-19,906,513</t>
+          <t>-75,042,144</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
     </row>
